--- a/resources/etsy/files/etsy-adv-liquidity-buffer.xlsx
+++ b/resources/etsy/files/etsy-adv-liquidity-buffer.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="7">
@@ -499,7 +499,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -589,7 +588,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -648,7 +646,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -681,7 +678,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
@@ -710,7 +706,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
@@ -774,7 +769,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>

--- a/resources/etsy/files/etsy-adv-liquidity-buffer.xlsx
+++ b/resources/etsy/files/etsy-adv-liquidity-buffer.xlsx
@@ -779,7 +779,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
